--- a/outputs/82-38.xlsx
+++ b/outputs/82-38.xlsx
@@ -349,100 +349,104 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -698,621 +702,621 @@
   <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="3" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>1650</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <f aca="false">F4*G4</f>
         <v>6600</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <f aca="false">SUM(H4)</f>
         <v>6600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <f aca="false">H5-H6</f>
         <v>6600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="13" t="n">
         <v>1650</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">F12*G12</f>
         <v>6600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="13" t="n">
         <f aca="false">F13*G13</f>
         <v>10000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="9" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="13" t="n">
         <f aca="false">SUM(H12:H13)</f>
         <v>16600</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="9" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="9" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="H16" s="13" t="n">
         <f aca="false">H14-H15</f>
         <v>16600</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="3" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <f aca="false">F21*G21</f>
         <v>8000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>1900</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <f aca="false">F22*G22</f>
         <v>9500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <f aca="false">SUM(H21:H22)</f>
         <v>17500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9" t="s">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <f aca="false">H23-H24</f>
         <v>17500</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="2" t="s">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="3" t="s">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <f aca="false">F30*G30</f>
         <v>8000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>2110</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <f aca="false">F31*G31</f>
         <v>4220</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>1900</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <f aca="false">F32*G32</f>
         <v>9500</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9" t="s">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <f aca="false">SUM(H30:H32)</f>
         <v>21720</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="8"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="9" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <f aca="false">H33-H34</f>
         <v>21720</v>
       </c>
@@ -1336,538 +1340,538 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="21" t="n">
+      <c r="I2" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="22" t="n">
         <v>1660</v>
       </c>
-      <c r="K2" s="21" t="n">
+      <c r="K2" s="22" t="n">
         <v>6640</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="21" t="n">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="22" t="n">
         <v>6640</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>1640</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <f aca="false">J4*I4</f>
         <v>6560</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <f aca="false">J5*I5</f>
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="21" t="n">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="22" t="n">
         <v>16560</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="C8" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>9500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="21" t="n">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="22" t="n">
         <v>17500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="C10" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <v>1980</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>7920</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>2110</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>4220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D13" s="20" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="21" t="n">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="22" t="n">
         <v>21690</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D15" s="20" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="21" t="n">
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="J16" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="K16" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="21" t="n">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
@@ -1890,538 +1894,538 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="21" t="n">
+      <c r="I2" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="22" t="n">
         <v>1660</v>
       </c>
-      <c r="K2" s="21" t="n">
+      <c r="K2" s="22" t="n">
         <v>6640</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="21" t="n">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="22" t="n">
         <v>6640</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="n">
+      <c r="A4" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>1640</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <f aca="false">J4*I4</f>
         <v>6560</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <f aca="false">J5*I5</f>
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="21" t="n">
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="22" t="n">
         <v>16560</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="C8" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>1900</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>9500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="21" t="n">
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="22" t="n">
         <v>17500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="C10" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <v>1980</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>7920</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>2110</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>4220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D13" s="20" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="21" t="n">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="22" t="n">
         <v>21690</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D15" s="20" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="21" t="n">
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="J16" s="22" t="n">
         <v>1910</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="K16" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19" t="n">
-        <v>45077</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20" t="n">
+        <v>45077</v>
+      </c>
+      <c r="D17" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="21" t="n">
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="22" t="n">
         <v>9550</v>
       </c>
     </row>
